--- a/data/raw/sales/Week 27/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 27/Audio_Array/other_channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 27\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3CEB7D-E744-4ADB-823D-BE94DC396E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51508C22-064D-4474-A75E-6BD0E89BFD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Audio Array" sheetId="4" r:id="rId1"/>
@@ -839,10 +839,10 @@
         <v>108</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="D2" s="7">
         <v>1</v>
@@ -859,10 +859,10 @@
         <v>111</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>113</v>
       </c>
       <c r="D3" s="7">
         <v>1</v>
@@ -879,10 +879,10 @@
         <v>114</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="D4" s="7">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>117</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="D5" s="7">
         <v>2</v>
@@ -919,10 +919,10 @@
         <v>18</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="D6" s="7">
         <v>2</v>
@@ -939,10 +939,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="D7" s="7">
         <v>1</v>
@@ -959,10 +959,10 @@
         <v>99</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="D8" s="7">
         <v>1</v>
@@ -979,10 +979,10 @@
         <v>121</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="D9" s="7">
         <v>1</v>
@@ -999,10 +999,10 @@
         <v>124</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="D10" s="7">
         <v>2</v>

--- a/data/raw/sales/Week 27/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 27/Audio_Array/other_channels.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 27\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51508C22-064D-4474-A75E-6BD0E89BFD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC12CA0C-EF6A-427B-9C93-3C7E42A143C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Audio Array" sheetId="4" r:id="rId1"/>
-    <sheet name="Blinkit Sales" sheetId="8" r:id="rId2"/>
-    <sheet name="B2B" sheetId="12" r:id="rId3"/>
+    <sheet name="Flipkart" sheetId="13" r:id="rId2"/>
+    <sheet name="Blinkit Sales" sheetId="8" r:id="rId3"/>
+    <sheet name="B2B" sheetId="12" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">B2B!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blinkit Sales'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">B2B!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blinkit Sales'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="201">
   <si>
     <t>SKU</t>
   </si>
@@ -418,13 +419,235 @@
   </si>
   <si>
     <t>B0G39ZHDYP</t>
+  </si>
+  <si>
+    <t>FBA79444</t>
+  </si>
+  <si>
+    <t>AM-W20</t>
+  </si>
+  <si>
+    <t>FBA75688</t>
+  </si>
+  <si>
+    <t>AM-W12</t>
+  </si>
+  <si>
+    <t>FBA79008</t>
+  </si>
+  <si>
+    <t>AI-06</t>
+  </si>
+  <si>
+    <t>FBA79104</t>
+  </si>
+  <si>
+    <t>AI-11</t>
+  </si>
+  <si>
+    <t>FBA75680</t>
+  </si>
+  <si>
+    <t>AM-C6</t>
+  </si>
+  <si>
+    <t>FBA76863</t>
+  </si>
+  <si>
+    <t>AI-03</t>
+  </si>
+  <si>
+    <t>FBA79010</t>
+  </si>
+  <si>
+    <t>AM-C42</t>
+  </si>
+  <si>
+    <t>FBA75676</t>
+  </si>
+  <si>
+    <t>AM-C4</t>
+  </si>
+  <si>
+    <t>FBA79106</t>
+  </si>
+  <si>
+    <t>AM-C44</t>
+  </si>
+  <si>
+    <t>FBA79016</t>
+  </si>
+  <si>
+    <t>AM-C3a</t>
+  </si>
+  <si>
+    <t>FBA75683</t>
+  </si>
+  <si>
+    <t>AA-03</t>
+  </si>
+  <si>
+    <t>FBA79448</t>
+  </si>
+  <si>
+    <t>AM-W35</t>
+  </si>
+  <si>
+    <t>FBA79356</t>
+  </si>
+  <si>
+    <t>AA-19WL</t>
+  </si>
+  <si>
+    <t>FBA75690</t>
+  </si>
+  <si>
+    <t>AM-C10</t>
+  </si>
+  <si>
+    <t>FBA78976</t>
+  </si>
+  <si>
+    <t>AA-22</t>
+  </si>
+  <si>
+    <t>FBA76597</t>
+  </si>
+  <si>
+    <t>AA-06</t>
+  </si>
+  <si>
+    <t>FBA79449</t>
+  </si>
+  <si>
+    <t>AM-W36</t>
+  </si>
+  <si>
+    <t>FBA75675</t>
+  </si>
+  <si>
+    <t>AM-C3</t>
+  </si>
+  <si>
+    <t>FBA79445</t>
+  </si>
+  <si>
+    <t>AM-W32</t>
+  </si>
+  <si>
+    <t>FBA78925</t>
+  </si>
+  <si>
+    <t>AM-C11X</t>
+  </si>
+  <si>
+    <t>FBA76414</t>
+  </si>
+  <si>
+    <t>AA-05</t>
+  </si>
+  <si>
+    <t>FBA79447</t>
+  </si>
+  <si>
+    <t>AM-W34</t>
+  </si>
+  <si>
+    <t>FBA75677</t>
+  </si>
+  <si>
+    <t>AM-C5</t>
+  </si>
+  <si>
+    <t>FBA78974</t>
+  </si>
+  <si>
+    <t>AA-20</t>
+  </si>
+  <si>
+    <t>FBA78973</t>
+  </si>
+  <si>
+    <t>AA-19</t>
+  </si>
+  <si>
+    <t>FBA79105</t>
+  </si>
+  <si>
+    <t>AI-12</t>
+  </si>
+  <si>
+    <t>FBA79064</t>
+  </si>
+  <si>
+    <t>AA-25</t>
+  </si>
+  <si>
+    <t>FBA78203</t>
+  </si>
+  <si>
+    <t>AM-C30</t>
+  </si>
+  <si>
+    <t>FBA76730</t>
+  </si>
+  <si>
+    <t>AM-C27</t>
+  </si>
+  <si>
+    <t>FBA75689</t>
+  </si>
+  <si>
+    <t>AM-W13</t>
+  </si>
+  <si>
+    <t>FBA75691</t>
+  </si>
+  <si>
+    <t>AM-W14</t>
+  </si>
+  <si>
+    <t>FBA79230</t>
+  </si>
+  <si>
+    <t>AM-W46</t>
+  </si>
+  <si>
+    <t>FBA78204</t>
+  </si>
+  <si>
+    <t>AM-C31</t>
+  </si>
+  <si>
+    <t>FBA78975</t>
+  </si>
+  <si>
+    <t>AA-21</t>
+  </si>
+  <si>
+    <t>FBA78424</t>
+  </si>
+  <si>
+    <t>AM-C37</t>
+  </si>
+  <si>
+    <t>FBA75681</t>
+  </si>
+  <si>
+    <t>AM-C7</t>
+  </si>
+  <si>
+    <t>FBA78961</t>
+  </si>
+  <si>
+    <t>AM-C40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,6 +688,11 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -498,7 +726,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -521,11 +749,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,6 +820,23 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1021,6 +1292,1002 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13AACAAE-4FB0-4CE2-90B5-8A607D857307}">
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="17">
+        <v>25</v>
+      </c>
+      <c r="D2" s="18">
+        <v>99351.694915254237</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="17">
+        <v>3</v>
+      </c>
+      <c r="D3" s="18">
+        <v>8405.9322033898316</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="17">
+        <v>11</v>
+      </c>
+      <c r="D4" s="18">
+        <v>24652.542372881358</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="17">
+        <v>4</v>
+      </c>
+      <c r="D5" s="18">
+        <v>11958.474576271186</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="17">
+        <v>5</v>
+      </c>
+      <c r="D6" s="18">
+        <v>10550.84745762712</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="17">
+        <v>0</v>
+      </c>
+      <c r="D7" s="18">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="17">
+        <v>0</v>
+      </c>
+      <c r="D8" s="18">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="17">
+        <v>2</v>
+      </c>
+      <c r="D9" s="18">
+        <v>5884.7457627118647</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="17">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="17">
+        <v>0</v>
+      </c>
+      <c r="D11" s="18">
+        <v>0</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="17">
+        <v>1</v>
+      </c>
+      <c r="D12" s="18">
+        <v>1322.0338983050849</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="17">
+        <v>0</v>
+      </c>
+      <c r="D13" s="18">
+        <v>0</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="17">
+        <v>1</v>
+      </c>
+      <c r="D14" s="18">
+        <v>1516.949152542373</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="17">
+        <v>2</v>
+      </c>
+      <c r="D15" s="18">
+        <v>6285.593220338983</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="17">
+        <v>3</v>
+      </c>
+      <c r="D16" s="18">
+        <v>6027.9661016949158</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="17">
+        <v>3</v>
+      </c>
+      <c r="D17" s="18">
+        <v>4772.8813559322034</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="17">
+        <v>1</v>
+      </c>
+      <c r="D18" s="18">
+        <v>1177.1186440677966</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="17">
+        <v>0</v>
+      </c>
+      <c r="D19" s="18">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="17">
+        <v>0</v>
+      </c>
+      <c r="D20" s="18">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="17">
+        <v>0</v>
+      </c>
+      <c r="D21" s="18">
+        <v>0</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="17">
+        <v>1</v>
+      </c>
+      <c r="D22" s="18">
+        <v>1641.5254237288136</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="17">
+        <v>0</v>
+      </c>
+      <c r="D23" s="18">
+        <v>0</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="17">
+        <v>1</v>
+      </c>
+      <c r="D24" s="18">
+        <v>423.72881355932208</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="17">
+        <v>0</v>
+      </c>
+      <c r="D25" s="18">
+        <v>0</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" s="17">
+        <v>0</v>
+      </c>
+      <c r="D26" s="18">
+        <v>0</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="17">
+        <v>0</v>
+      </c>
+      <c r="D27" s="18">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="18">
+        <v>2980.5084745762715</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="17">
+        <v>0</v>
+      </c>
+      <c r="D29" s="18">
+        <v>0</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="17">
+        <v>0</v>
+      </c>
+      <c r="D30" s="18">
+        <v>0</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="17">
+        <v>0</v>
+      </c>
+      <c r="D31" s="18">
+        <v>0</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="17">
+        <v>0</v>
+      </c>
+      <c r="D32" s="18">
+        <v>0</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="17">
+        <v>1</v>
+      </c>
+      <c r="D33" s="18">
+        <v>3493.2203389830511</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="17">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18">
+        <v>1382.2033898305085</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" s="17">
+        <v>2</v>
+      </c>
+      <c r="D35" s="18">
+        <v>6164.406779661017</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="17">
+        <v>0</v>
+      </c>
+      <c r="D36" s="18">
+        <v>0</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" s="17">
+        <v>2</v>
+      </c>
+      <c r="D37" s="18">
+        <v>6013.5593220338988</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="17">
+        <v>0</v>
+      </c>
+      <c r="D38" s="18">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="17">
+        <v>0</v>
+      </c>
+      <c r="D39" s="18">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C40" s="17">
+        <v>0</v>
+      </c>
+      <c r="D40" s="18">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="17">
+        <v>0</v>
+      </c>
+      <c r="D41" s="18">
+        <v>0</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C42" s="17">
+        <v>0</v>
+      </c>
+      <c r="D42" s="18">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C43" s="17">
+        <v>0</v>
+      </c>
+      <c r="D43" s="18">
+        <v>0</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C44" s="17">
+        <v>0</v>
+      </c>
+      <c r="D44" s="18">
+        <v>0</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C45" s="17">
+        <v>0</v>
+      </c>
+      <c r="D45" s="18">
+        <v>0</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46" s="17">
+        <v>0</v>
+      </c>
+      <c r="D46" s="18">
+        <v>0</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="17">
+        <v>0</v>
+      </c>
+      <c r="D47" s="18">
+        <v>0</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C48" s="17">
+        <v>0</v>
+      </c>
+      <c r="D48" s="18">
+        <v>0</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" s="17">
+        <v>0</v>
+      </c>
+      <c r="D49" s="18">
+        <v>0</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="17">
+        <v>0</v>
+      </c>
+      <c r="D50" s="18">
+        <v>0</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="17">
+        <v>1</v>
+      </c>
+      <c r="D51" s="18">
+        <v>4236.4406779661022</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C52" s="17">
+        <v>0</v>
+      </c>
+      <c r="D52" s="18">
+        <v>0</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="17">
+        <v>1</v>
+      </c>
+      <c r="D53" s="18">
+        <v>1894.0677966101696</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="C54" s="17">
+        <v>0</v>
+      </c>
+      <c r="D54" s="18">
+        <v>0</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" s="17">
+        <v>0</v>
+      </c>
+      <c r="D55" s="18">
+        <v>0</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="C56" s="17">
+        <v>0</v>
+      </c>
+      <c r="D56" s="18">
+        <v>0</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C57" s="17">
+        <v>0</v>
+      </c>
+      <c r="D57" s="18">
+        <v>0</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="17">
+        <v>0</v>
+      </c>
+      <c r="D58" s="18">
+        <v>0</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:X880"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2128,7 +3395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AA720"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
